--- a/Products/Анализ_5_ниш_US_UK_DE_AE_20260706.xlsx
+++ b/Products/Анализ_5_ниш_US_UK_DE_AE_20260706.xlsx
@@ -7,18 +7,19 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ТОП-50 ходовые" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Новинки с 02.2026" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Все товары (241)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Запуск ОАЭ (расчёт)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Комиссии и тарифы" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Методика и оговорки" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Выводы" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ТОП-50 ходовые" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Новинки с 02.2026" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Все товары (241)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Запуск ОАЭ (расчёт)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Комиссии и тарифы" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Методика и оговорки" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ТОП-50 ходовые'!$A$1:$AD$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Новинки с 02.2026'!$A$1:$AD$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Все товары (241)'!$A$1:$AD$240</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Запуск ОАЭ (расчёт)'!$A$1:$U$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ТОП-50 ходовые'!$A$1:$AD$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Новинки с 02.2026'!$A$1:$AD$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Все товары (241)'!$A$1:$AD$240</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Запуск ОАЭ (расчёт)'!$A$1:$U$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +49,10 @@
     <font>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="6">
@@ -104,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -128,6 +133,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -493,6 +499,188 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>ВЫВОДЫ И РЕКОМЕНДАЦИИ (06.07.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1. РЫНОК ЗАПУСКА: ОАЭ — лучшая юнит-экономика из четырёх рынков.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Пошлина 5%, VAT 5%, дешёвый морской фрахт через Jebel Ali (~$1.9/кг), FBA 7.2–19.5 AED/юнит.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Германия — второй рынок (пошлина ~4%, но VAT 19% и фрахт дороже). Лист «Запуск ОАЭ (расчёт)» — готовый шорт-лист.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2. США — ТОЛЬКО ИНДИКАТОР СПРОСА, НЕ РЫНОК ЗАПУСКА: при пошлине ~35% на китайский импорт</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   23 из 50 бестселлеров уходят в минус при типовой закупочной цене (красные строки в «ТОП-50»).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3. КАТЕГОРИИ ДЛЯ ВХОДА С НУЛЯ (по убыванию привлекательности):</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Подушки на сиденье — FOB $2.5–5.5, маржа до 60%, лидер (Everlasting Comfort) продаёт ~20 000 шт/мес в US.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Валидированный спрос на всех рынках. Вход: гелевые/memory foam, цена $25–45 (90–190 AED).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Desk pads (PU-кожа) — FOB $1.5–4, маржа 25–40%, низкий вес = дешёвая логистика.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Новинка-пример: YSAGi масштабируется в DE/UK с мая 2026 (~4 600 шт/мес).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Обувницы — стабильный спрос (до 9 000 шт/мес US), FOB $4–15; выбирать лёгкие металлические этажерки, не шкафы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Коврики под кресло — средний спрос, тяжёлые (вес режет маржу) — брать только рулонные PVC до 4 кг.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Льдогенераторы — только премиум (nugget ice) и только ОАЭ/DE: GE Opal (новинка 03.2026) даёт маржу 43%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     при закупке ≤$109. Базовые bullet-модели на грани рентабельности. В ОАЭ обязательна сертификация ESMA/ECAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>4. ПОТОЛОК ЗАКУПКИ: колонка «Закупка МАКС (FOB $)» в каждом листе — максимум, который можно платить</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   поставщику за юнит, чтобы чистая маржа была ≥25% после ВСЕХ затрат. Если типовая FOB Alibaba выше — торговаться или пропускать.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>5. НОВИНКИ С ФЕВРАЛЯ 2026 (лист «Новинки»): 16 позиций BUY с подтверждёнными продажами.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Тренды: nugget ice makers, водостойкие PU desk mats, гелевые подушки, дверные органайзеры для обуви.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>6. ОГОВОРКИ: Keepa не покрывает amazon.ae — спрос/цены ОАЭ = проекция UK/DE (+8% премия), комиссии по rate card</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   sell.amazon.ae. Ссылки Alibaba поисковые: MOQ, цену и сертификаты (CE/UKCA/ESMA) проверять у поставщика.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AD50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6038,7 +6226,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11539,7 +11727,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26541,7 +26729,7 @@
         <v>-0.1</v>
       </c>
       <c r="Z143" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA143" s="4" t="inlineStr">
         <is>
@@ -28773,7 +28961,7 @@
         <v>-0.1</v>
       </c>
       <c r="Z164" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA164" s="4" t="inlineStr">
         <is>
@@ -29189,7 +29377,7 @@
         <v>-0.1</v>
       </c>
       <c r="Z168" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA168" s="4" t="inlineStr">
         <is>
@@ -29813,7 +30001,7 @@
         <v>-0.1</v>
       </c>
       <c r="Z174" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA174" s="4" t="inlineStr">
         <is>
@@ -29917,7 +30105,7 @@
         <v>-0.1</v>
       </c>
       <c r="Z175" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA175" s="4" t="inlineStr">
         <is>
@@ -37234,7 +37422,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -41154,7 +41342,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -41617,7 +41805,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -41636,9 +41824,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
